--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128733482</v>
       </c>
       <c r="B2" t="n">
-        <v>58406</v>
+        <v>58433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128733481</v>
       </c>
       <c r="B3" t="n">
-        <v>58366</v>
+        <v>58393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128733471</v>
       </c>
       <c r="B4" t="n">
-        <v>57847</v>
+        <v>57874</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>128733472</v>
       </c>
       <c r="B5" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128733482</v>
       </c>
       <c r="B2" t="n">
-        <v>58433</v>
+        <v>58437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128733481</v>
       </c>
       <c r="B3" t="n">
-        <v>58393</v>
+        <v>58397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128733471</v>
       </c>
       <c r="B4" t="n">
-        <v>57874</v>
+        <v>57878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>128733472</v>
       </c>
       <c r="B5" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128733482</v>
       </c>
       <c r="B2" t="n">
-        <v>58437</v>
+        <v>58440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128733481</v>
       </c>
       <c r="B3" t="n">
-        <v>58397</v>
+        <v>58400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128733471</v>
       </c>
       <c r="B4" t="n">
-        <v>57878</v>
+        <v>57881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>128733472</v>
       </c>
       <c r="B5" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104119</v>
+        <v>104124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104124</v>
+        <v>104127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128733482</v>
       </c>
       <c r="B2" t="n">
-        <v>58440</v>
+        <v>58442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128733481</v>
       </c>
       <c r="B3" t="n">
-        <v>58400</v>
+        <v>58402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128733471</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>128733472</v>
       </c>
       <c r="B5" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104127</v>
+        <v>104137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104137</v>
+        <v>104144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128733482</v>
       </c>
       <c r="B2" t="n">
-        <v>58442</v>
+        <v>58444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128733481</v>
       </c>
       <c r="B3" t="n">
-        <v>58402</v>
+        <v>58404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128733471</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>128733472</v>
       </c>
       <c r="B5" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104144</v>
+        <v>104146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104146</v>
+        <v>104172</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104172</v>
+        <v>104174</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104174</v>
+        <v>104175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104175</v>
+        <v>104179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104179</v>
+        <v>104181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104181</v>
+        <v>104185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104185</v>
+        <v>104195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129107699</v>
       </c>
       <c r="B6" t="n">
-        <v>104195</v>
+        <v>104198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45595-2025 artfynd.xlsx
+++ b/artfynd/A 45595-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128733482</v>
+        <v>77192214</v>
       </c>
       <c r="B2" t="n">
-        <v>58444</v>
+        <v>56888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100041</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,23 +708,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hjälmängen, Srm</t>
+          <t>Tegelvreten infart, Tegelvreten, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660444</v>
+        <v>660450</v>
       </c>
       <c r="R2" t="n">
-        <v>6554726</v>
+        <v>6554756</v>
       </c>
       <c r="S2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +757,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Låg helt orörlig och seg på grusvägen. Troligen led den av uttorkning (extremt varm och torr period)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,28 +786,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Magnus Lindgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Magnus Lindgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128733481</v>
+        <v>128733472</v>
       </c>
       <c r="B3" t="n">
-        <v>58404</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,16 +816,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,7 +840,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -868,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +927,7 @@
         <v>128733471</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128733472</v>
+        <v>128733481</v>
       </c>
       <c r="B5" t="n">
-        <v>58097</v>
+        <v>58636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,16 +1054,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,11 +1078,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1106,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,48 +1158,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129107699</v>
+        <v>128733482</v>
       </c>
       <c r="B6" t="n">
-        <v>104198</v>
+        <v>58676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tegelvreten, Srm</t>
+          <t>Hjälmängen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660479</v>
+        <v>660444</v>
       </c>
       <c r="R6" t="n">
-        <v>6554601</v>
+        <v>6554726</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,12 +1231,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,15 +1261,112 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129107699</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tegelvreten, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>660479</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6554601</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
